--- a/mosip_master/xlsx/template_type.xlsx
+++ b/mosip_master/xlsx/template_type.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="28429"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="28526"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\tf_nira\mosip-data\mosip_master\xlsx\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\TF-NIRA-REPOS\mosip-data\mosip_master\xlsx\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C732552D-6DBE-466E-9E7A-9AE0A1F55596}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{83EE52D2-5A79-4A5B-A566-2643F2202AE0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Worksheet" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7120" uniqueCount="722">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7132" uniqueCount="728">
   <si>
     <t>code</t>
   </si>
@@ -2186,6 +2186,24 @@
   </si>
   <si>
     <t>Preview generated after registration COP</t>
+  </si>
+  <si>
+    <t>RPR_TEC_ISSUE_ERROR_EMAIL</t>
+  </si>
+  <si>
+    <t>RPR_TEC_ISSUE_ERROR_EMAIL_SUB</t>
+  </si>
+  <si>
+    <t>RPR_TEC_ISSUE_ERROR_SMS</t>
+  </si>
+  <si>
+    <t>Template for technical issue with error Email</t>
+  </si>
+  <si>
+    <t>Template for technical issue with error Subject</t>
+  </si>
+  <si>
+    <t>Template for technical issue with error SMS</t>
   </si>
 </sst>
 </file>
@@ -2552,11 +2570,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D1780"/>
+  <dimension ref="A1:D1783"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="43.28515625" customWidth="1"/>
-    <col min="2" max="2" width="29.7109375" customWidth="1"/>
+    <col min="2" max="2" width="62.85546875" customWidth="1"/>
     <col min="3" max="3" width="21.28515625" customWidth="1"/>
     <col min="4" max="4" width="24" customWidth="1"/>
   </cols>
@@ -27481,6 +27499,48 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1781" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1781" t="s">
+        <v>722</v>
+      </c>
+      <c r="B1781" t="s">
+        <v>725</v>
+      </c>
+      <c r="C1781" t="s">
+        <v>6</v>
+      </c>
+      <c r="D1781" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1782" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1782" t="s">
+        <v>723</v>
+      </c>
+      <c r="B1782" t="s">
+        <v>726</v>
+      </c>
+      <c r="C1782" t="s">
+        <v>6</v>
+      </c>
+      <c r="D1782" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1783" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1783" t="s">
+        <v>724</v>
+      </c>
+      <c r="B1783" t="s">
+        <v>727</v>
+      </c>
+      <c r="C1783" t="s">
+        <v>6</v>
+      </c>
+      <c r="D1783" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <sheetProtection formatCells="0" formatColumns="0" formatRows="0" insertColumns="0" insertRows="0" insertHyperlinks="0" deleteColumns="0" deleteRows="0" sort="0" autoFilter="0" pivotTables="0"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
